--- a/data/mapping/diagnosis_adrg_mapping.xlsx
+++ b/data/mapping/diagnosis_adrg_mapping.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C276"/>
+  <dimension ref="A1:C366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4817,300 +4817,1778 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>방광의 악성 신생물</t>
+          <t>어지럼증 및 어지럼</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>L631</t>
+          <t>B770</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Kidney and Urinary Tract Neoplasms with</t>
+          <t>Concussion</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>자궁체부의 악성 신생물</t>
+          <t>어깨 및 위팔의 골절</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>K601</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr"/>
+          <t>I130</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Surgery of Shoulder and Humerus Fracture</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>기타 특정 관절장애</t>
+          <t>편도 및 아데노이드의 만성 질환</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>I740</t>
+          <t>D680</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Injuries to Forearm, Wrist, Hand and Foot,</t>
+          <t>Pharyngitis and Tonsillitis</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>직장구불결장접합부의 악성 신생물</t>
+          <t>비뇨계통의 기타 장애</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>G041</t>
+          <t>L640</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Rectal Resection, Transanal or Transsacral Approach for Malignancy</t>
+          <t>Lower Urinary Tract Infections, Age ＜65</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>기타 신세뇨관-간질질환</t>
+          <t>기타 추간판장애</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>L621</t>
+          <t>B054</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Non-Infectious Kidney Diseases with</t>
+          <t>Spinal Fusion with Myelopathy</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>항문 및 항문관의 악성 신생물</t>
+          <t>만성 허혈심장병</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>G041</t>
+          <t>F662</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Rectal Resection, Transanal or Transsacral Approach for Malignancy</t>
+          <t>Peripheral Arterial Occlusive Disease with</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>질 및 외음부의 기타 염증</t>
+          <t>어깨병변</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>N610</t>
+          <t>I150</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Female Reproductive System Infections</t>
+          <t>Other Shoulder Procedures</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>우울에피소드</t>
+          <t>발진티푸스</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>U630</t>
+          <t>T013</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Affective Disorders, Age ≥65</t>
+          <t>OR Procedures for Other Infectious Diseases</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>욕창궤양 및 압박부위</t>
+          <t>코 및 비동의 기타 장애</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>J021</t>
+          <t>D660</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Flap for Skin Ulcer or Cellulitis</t>
+          <t>Other Nose Diseases</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>코용종</t>
+          <t>췌장의 악성 신생물</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>D680</t>
+          <t>H623</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Paranasal Sinus Infections and</t>
+          <t>Hepatobiliary Diagnostic Procedures for Malignancy</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>출혈 또는 경색증으로 명시되지 않은 뇌졸중</t>
+          <t>급성 심근경색증</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>B701</t>
+          <t>F600</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Injury of Root, Plexus and Nerves of Trunk</t>
+          <t>Percutaneous Coronary Artery Procedures</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>자연유산</t>
+          <t>대상포진</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>O610</t>
+          <t>B730</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Abortion without D&amp;C or Aspiration</t>
+          <t>Encephalitis except Viral Meningitis</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>기타 살모넬라감염</t>
+          <t>무릎의 관절 및 인대의 탈구, 염좌 및 긴장</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>G671</t>
+          <t>I164</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Enteritis</t>
+          <t>Other Knee Joint Procedures</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>자궁의 평활근종</t>
+          <t>기타 척추병증</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>N620</t>
+          <t>B054</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Menstrual and Other Female Reproductive</t>
+          <t>Spinal Fusion with Myelopathy</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>달리 분류되지 않은 처치의 합병증</t>
+          <t>장의 혈관장애</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>X630</t>
+          <t>G673</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Complications of Treatment</t>
+          <t>Vascular Disorders of Intestine</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>바이러스성 및 기타 명시된 장감염</t>
+          <t>유방의 양성 신생물</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>G671</t>
+          <t>J032</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Enteritis</t>
+          <t>Mastectomy except Malignancy</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>내부 정형외과적 인공삽입장치, 삽입물 및 이식편의 합병증</t>
+          <t>위궤양</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>I730</t>
+          <t>G501</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Aftercare of Musculoskeletal Disorders</t>
+          <t>Sigmoidoscopy for Major Digestive Diseases</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
+          <t>팔의 단일신경병증</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>B780</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Peripheral Nerve Disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>전립선의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>L623</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>전립선 수술 (악성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>치핵 및 항문주위정맥혈전증</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>G684</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Diseases of Anus</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>편도주위농양</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D680</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>편도 및 인두 감염</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>담도의 기타 및 상세불명 부분의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>H623</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Hepatobiliary Diagnostic Procedures for Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>발작성 빈맥</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>F711</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Tachycardia</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>무릎의 내부장애</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>I164</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Other Knee Joint Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>기타 청력소실</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D620</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Hearing Impairment, Age ≤18</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>방광의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>L631</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Kidney and Urinary Tract Neoplasms with</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 바이러스폐렴</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>E612</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Viral Pneumonia, Adult(18＜Age＜65)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>유방의 제자리암종</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>J032</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Open Minor Breast Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>항뇌전증제, 진정제-수면제 및 항파킨슨제에 의한 중독</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>X620</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>방광염</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>L640</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Lower Urinary Tract Infections, Age ＜65</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>동맥 및 세동맥의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>F662</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Other Vascular Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>근육의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>I690</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Gout and Specific Arthropathies</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>식도의 기타 질환</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>G501</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Sigmoidoscopy for Major Digestive Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>급성 A형간염</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>H641</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis with Complications</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>기타 심장부정맥</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>F711</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Tachycardia</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>상세불명의 혈뇨</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>L650</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Kidney and Urinary Tract Signs and</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>자궁체부의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>K601</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>기타 특정 관절장애</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>I740</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Injuries to Forearm, Wrist, Hand and Foot,</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>단핵구성 백혈병</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>G603</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>골수형성이상증후군</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>G603</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>이식장치의 조정 및 관리를 위하여 보건서비스와 접하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>F750</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Other Circulatory System Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>기타 및 상세불명 부위의 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>X630</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>윤활막 및 힘줄의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>I163</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Humerus, Tibia, and Fibula Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>섬유모세포장애</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>I221</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Major Wrist and Hand Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>병적 골절을 동반한 골다공증</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>I690</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>기타 비감염성 위장염 및 결장염</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>G640</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Other Major Digestive system Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 호흡부전</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>E660</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Respiratory Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>기타 및 상세불명의 원인에 의한 수막염</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>B701</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Other Nervous System Infection except</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>기타 형태의 마이코박테리아에 의한 감염</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>E611</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Respiratory Tuberculosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>뇌전증</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>B744</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Other Seizure, Age ≤18</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>유방의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>J032</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Open Minor Breast Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>기타 비독성 고이터</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>K650</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Other Thyroid Disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>삼차신경의 장애</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>B701</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Cranial Nerve Disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 간부전</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>H641</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Other Hepatitis with Complications</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>직장구불결장접합부의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>G041</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Rectal Resection, Transanal or Transsacral Approach for Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>음낭수종 및 정액류</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>L672</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>기타 신세뇨관-간질질환</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>L621</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Non-Infectious Kidney Diseases with</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>고관절의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>I630</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>기타 윤활낭병증</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>I690</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Gout and Specific Arthropathies</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>헤르페스바이러스[단순헤르페스] 감염</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>J650</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>기타 신체구조의 진단영상검사상 이상소견</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>X640</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>복벽탈장</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>G684</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Other Digestive system Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>갑상선염</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>K650</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Other Thyroid Disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>항문 및 항문관의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>G041</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Rectal Resection, Transanal or Transsacral Approach for Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>비뇨 및 골반 기관의 손상</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>L672</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Other Kidney and Urinary Tract Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>연골의 기타 장애</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>I690</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Gout and Specific Arthropathies</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>기타 말초혈관질환</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>F662</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Other Vascular Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>저혈압</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>F750</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Other Circulatory System Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>중이 및 호흡계통의 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>E631</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Respiratory Neoplasm with Radiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>뇌 및 중추신경계통의 행동양식 불명 또는 미상의 신생물</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>B018</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>CNS Stereotactic Procedures in Brain Tumor and Other Creation of Lesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>기타 다발신경병증</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>B780</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Peripheral Nerve Disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>식품으로 섭취한 기타 유해물질의 독성효과</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>X620</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>유방의 상세불명의 덩이</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>J650</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>유방의 기타 질환</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>기타 내부 인공삽입장치, 삽입물 및 이식편의 합병증</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>X630</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>비뇨생식기 인공삽입장치, 삽입물 및 이식편의 합병증</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>L672</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Other Kidney and Urinary Tract Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>질 및 외음부의 기타 염증</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>N610</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Female Reproductive System Infections</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>팔꿈치의 관절 및 인대의 탈구, 염좌 및 긴장</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>I130</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Surgery of Forearm Fracture</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>기타 골부착부병증</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>I222</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Minor Wrist and Hand Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>폐부종</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>E660</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Respiratory Failure</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>유방의 염증성 장애</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>J650</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>유방 감염/염증</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>유방의 비대</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>J032</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Open Minor Breast Procedures</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>우울에피소드</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>U630</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Affective Disorders, Age ≥65</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>유방의 선천기형</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>J032</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Mastectomy except Malignancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>욕창궤양 및 압박부위</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>J021</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Flap for Skin Ulcer or Cellulitis</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>위공장궤양</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>G501</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Sigmoidoscopy for Major Digestive Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>갑상선독증[갑상선기능항진증]</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>K650</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Thyrotoxicosis</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>이상동(梨狀洞)의 악성 신생물</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>미매핑</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>인공개구에 대한 관리를 위하여 보건서비스와 접하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>E680</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Other Respiratory System Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>호흡의 이상</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>D640</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Allergic Rhinitis</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>혈청검사양성 류마티스관절염</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>F662</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Other Vascular Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>혈관운동성 및 알레르기성 비염</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>D680</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Non-Allergic Rhinitis</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>피부의 악성 흑색종</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>J081</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>티눈 및 굳은살</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>J700</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>피부의 기타 질환</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>투석을 포함한 치료를 위하여 보건서비스와 접하고 있는 사람</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>L610</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Chronic Renal Failure, Peritoneal Dialysis,</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>코용종</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>D680</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Paranasal Sinus Infections and</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>출혈 또는 경색증으로 명시되지 않은 뇌졸중</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>B701</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Injury of Root, Plexus and Nerves of Trunk</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>중이의 진주종</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>D620</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Inner and Middle Ear Infections and</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>자연유산</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>O610</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Abortion without D&amp;C or Aspiration</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>기타 뇌혈관질환</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>B780</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Other Cerebrovascular Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>기타 살모넬라감염</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>G671</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Enteritis</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>자궁의 평활근종</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>N620</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Menstrual and Other Female Reproductive</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>기타 및 부위불명의 소화계통의 양성 신생물</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>G684</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Other Digestive System Diseases</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>사타구니탈장</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>G684</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Open Inguinal and Femoral Hernia</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>실신 및 허탈</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>F730</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Syncope and Collapse</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>달리 분류되지 않은 처치의 합병증</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>X630</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Complications of Treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>바이러스성 및 기타 명시된 장감염</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>G671</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Enteritis</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>내부 정형외과적 인공삽입장치, 삽입물 및 이식편의 합병증</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>I730</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Aftercare of Musculoskeletal Disorders</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
           <t>요추 및 골반의 관절 및 인대의 탈구, 염좌 및 긴장</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr">
+      <c r="B366" t="inlineStr">
         <is>
           <t>I681</t>
         </is>
       </c>
-      <c r="C276" t="inlineStr">
+      <c r="C366" t="inlineStr">
         <is>
           <t>Non-Surgical Neck and Back Conditions</t>
         </is>
